--- a/data/semesters/sem1/courses.xlsx
+++ b/data/semesters/sem1/courses.xlsx
@@ -1018,7 +1018,11 @@
           <t>CE100-A,CE100-B</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1270,7 +1274,11 @@
           <t>CE100-A,CE100-B</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1390,7 +1398,11 @@
         <v>0</v>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1451,7 +1463,11 @@
           <t>CV200-A,CV200-B</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1577,7 +1593,11 @@
           <t>CE200-A,CE200-B</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -1896,7 +1916,11 @@
           <t>CE200-A,CE200-B</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -2408,7 +2432,11 @@
           <t>CE300-A,CE300-B</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -2597,7 +2625,11 @@
           <t>CE300-A,CE300-B</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -2975,7 +3007,11 @@
           <t>CE400-A,CE400-B</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -3231,7 +3267,11 @@
           <t>CE400-A,CE400-B</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -3546,7 +3586,11 @@
           <t>CE400-A,CE400-B</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -4062,7 +4106,11 @@
           <t>CV100-A,CV100-B</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -4377,7 +4425,11 @@
           <t>CV200-A,CV200-B</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4503,7 +4555,11 @@
           <t>CV200-A,CV200-B</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4566,7 +4622,11 @@
           <t>CV200-A,CV200-B</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
@@ -5267,7 +5327,11 @@
           <t>CV300-A,CV300-B</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
@@ -5706,7 +5770,11 @@
         <v>0</v>
       </c>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
@@ -5769,7 +5837,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
@@ -5832,7 +5904,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
@@ -5895,7 +5971,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr"/>
@@ -6021,7 +6101,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr"/>
@@ -6261,7 +6345,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr"/>
@@ -6387,7 +6475,11 @@
           <t>DS200-A</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
@@ -6450,7 +6542,11 @@
           <t>DS200-A</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
@@ -6828,7 +6924,11 @@
           <t>DS200-A</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
@@ -7537,7 +7637,11 @@
           <t>EL200-A,EL200-B</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
@@ -7600,7 +7704,11 @@
           <t>EL200-A,EL200-B</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
@@ -9699,7 +9807,11 @@
           <t>ES100-A,ES100-B</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
@@ -9762,7 +9874,11 @@
           <t>ES200-A,ES200-B</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
@@ -9959,7 +10075,11 @@
           <t>ES200-A,ES200-B</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr"/>
@@ -10022,7 +10142,11 @@
           <t>ES200-A,ES200-B</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
@@ -10660,7 +10784,11 @@
           <t>ES300-A,ES300-B</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
@@ -11264,7 +11392,11 @@
           <t>ES400-A,ES400-B</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
@@ -11654,7 +11786,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
@@ -11906,7 +12042,11 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
@@ -12032,7 +12172,11 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
@@ -12095,7 +12239,11 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
@@ -12221,7 +12369,11 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
@@ -13127,7 +13279,11 @@
         <v>0</v>
       </c>
       <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
@@ -13850,7 +14006,11 @@
           <t>TM100-A</t>
         </is>
       </c>
-      <c r="P211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr"/>
@@ -15436,7 +15596,11 @@
         <v>0</v>
       </c>
       <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
@@ -15493,7 +15657,11 @@
         <v>0</v>
       </c>
       <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
@@ -18940,7 +19108,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr"/>
@@ -19192,7 +19364,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P293" t="inlineStr"/>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q293" t="inlineStr"/>
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr"/>
@@ -19255,7 +19431,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P294" t="inlineStr"/>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q294" t="inlineStr"/>
       <c r="R294" t="inlineStr"/>
       <c r="S294" t="inlineStr"/>
@@ -19444,7 +19624,11 @@
           <t>TM100-A</t>
         </is>
       </c>
-      <c r="P297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q297" t="inlineStr"/>
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr"/>
@@ -19507,7 +19691,11 @@
           <t>TM100-A</t>
         </is>
       </c>
-      <c r="P298" t="inlineStr"/>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q298" t="inlineStr"/>
       <c r="R298" t="inlineStr"/>
       <c r="S298" t="inlineStr"/>
@@ -19570,7 +19758,11 @@
           <t>TM100-A</t>
         </is>
       </c>
-      <c r="P299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q299" t="inlineStr"/>
       <c r="R299" t="inlineStr"/>
       <c r="S299" t="inlineStr"/>

--- a/data/semesters/sem1/courses.xlsx
+++ b/data/semesters/sem1/courses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S300"/>
+  <dimension ref="A1:S297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6176,17 +6176,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DS 169</t>
+          <t>TM 169</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DS 169</t>
+          <t>TM 169</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -6233,17 +6233,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TM 169</t>
+          <t>DS 173</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TM 169</t>
+          <t>DS 173</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -6252,11 +6252,11 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AMPOFI</t>
+          <t>Dr A. A. Amponsah</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6275,14 +6275,24 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
-      </c>
-      <c r="M91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
       <c r="N91" t="n">
         <v>0</v>
       </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>DS100-A</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr"/>
@@ -6309,21 +6319,21 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dr A. A. Amponsah</t>
+          <t>AMPOMAH</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6332,7 +6342,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
         <v>1</v>
@@ -6345,11 +6355,7 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr"/>
@@ -6357,12 +6363,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DS 173</t>
+          <t>DS 251</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DS 173</t>
+          <t>DS 251</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6371,26 +6377,26 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AMPOMAH</t>
+          <t>I. Kwofie</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6409,10 +6415,14 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>DS100-A</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
+          <t>DS200-A</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
@@ -6420,12 +6430,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DS 251</t>
+          <t>DS 255</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DS 251</t>
+          <t>DS 255</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6439,11 +6449,11 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>I. Kwofie</t>
+          <t>ADU-GYEMFI</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -6462,7 +6472,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
@@ -6510,17 +6520,17 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6529,7 +6539,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
         <v>1</v>
@@ -6542,11 +6552,7 @@
           <t>DS200-A</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
@@ -6554,12 +6560,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DS 255</t>
+          <t>DS 265</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DS 255</t>
+          <t>DS 265</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6573,14 +6579,14 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ADU-GYEMFI</t>
+          <t>Assoc Prof J. Acquah</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -6599,7 +6605,7 @@
         <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -6617,12 +6623,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DS 265</t>
+          <t>DS 271</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DS 265</t>
+          <t>DS 271</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6636,11 +6642,11 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Assoc Prof J. Acquah</t>
+          <t>AMPOMAH</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -6662,7 +6668,7 @@
         <v>2</v>
       </c>
       <c r="M97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -6680,12 +6686,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DS 271</t>
+          <t>DS 275</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DS 271</t>
+          <t>DS 275</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6699,7 +6705,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AMPOMAH</t>
+          <t>Owusu-Bempah</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -6743,12 +6749,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DS 275</t>
+          <t>DS 277</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DS 275</t>
+          <t>DS 277</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6762,11 +6768,11 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Owusu-Bempah</t>
+          <t>E. Obu</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -6788,7 +6794,7 @@
         <v>2</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
@@ -6806,12 +6812,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DS 277</t>
+          <t>DS 279</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DS 277</t>
+          <t>DS 279</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6825,11 +6831,11 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>E. Obu</t>
+          <t>NKETSIA</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -6839,7 +6845,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6851,7 +6857,7 @@
         <v>2</v>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -6861,7 +6867,11 @@
           <t>DS200-A</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
@@ -6869,30 +6879,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DS 279</t>
+          <t>EL 141</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DS 279</t>
+          <t>EL 141</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NKETSIA</t>
+          <t>ADZAKOR</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -6902,7 +6912,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6911,7 +6921,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
         <v>1</v>
@@ -6921,7 +6931,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>DS200-A</t>
+          <t>EL100-A,EL100-B</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -6936,12 +6946,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EL 141</t>
+          <t>EL 151</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EL 141</t>
+          <t>EL 151</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6955,11 +6965,11 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ADZAKOR</t>
+          <t>Dr G. Owusu</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -6978,7 +6988,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M102" t="n">
         <v>1</v>
@@ -6991,11 +7001,7 @@
           <t>EL100-A,EL100-B</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr"/>
@@ -7026,10 +7032,10 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -7066,12 +7072,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EL 151</t>
+          <t>EL 155</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EL 151</t>
+          <t>EL 155</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7085,14 +7091,14 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dr G. Owusu</t>
+          <t>E. Adu Kyeremeh</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -7129,12 +7135,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EL 155</t>
+          <t>EL 157</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EL 155</t>
+          <t>EL 157</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7148,11 +7154,11 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>E. Adu Kyeremeh</t>
+          <t>E. ARHINFUL</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -7171,7 +7177,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
         <v>1</v>
@@ -7184,7 +7190,11 @@
           <t>EL100-A,EL100-B</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
@@ -7192,12 +7202,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EL 157</t>
+          <t>EL 159</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EL 157</t>
+          <t>EL 159</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7211,7 +7221,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>E. ARHINFUL</t>
+          <t>Dr A. A. Amponsah</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -7225,7 +7235,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7259,12 +7269,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EL 159</t>
+          <t>EL 163</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EL 159</t>
+          <t>EL 163</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7278,11 +7288,11 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dr A. A. Amponsah</t>
+          <t>E. Obu</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -7292,7 +7302,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7301,7 +7311,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M107" t="n">
         <v>1</v>
@@ -7314,11 +7324,7 @@
           <t>EL100-A,EL100-B</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
@@ -7326,12 +7332,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EL 163</t>
+          <t>EL 167</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EL 163</t>
+          <t>EL 167</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7345,11 +7351,11 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>E. Obu</t>
+          <t>J. Ellis</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -7371,7 +7377,7 @@
         <v>2</v>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
@@ -7389,12 +7395,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EL 167</t>
+          <t>EL 169</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EL 167</t>
+          <t>EL 169</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7408,11 +7414,11 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>J. Ellis</t>
+          <t>AMPOFI</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -7434,7 +7440,7 @@
         <v>2</v>
       </c>
       <c r="M109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
@@ -7452,12 +7458,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EL 169</t>
+          <t>EL 171</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EL 169</t>
+          <t>EL 171</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7471,11 +7477,11 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AMPOFI</t>
+          <t>S. K. Dankwah</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -7494,7 +7500,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
         <v>1</v>
@@ -7507,7 +7513,11 @@
           <t>EL100-A,EL100-B</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
@@ -7515,12 +7525,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EL 171</t>
+          <t>EL 251</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EL 171</t>
+          <t>EL 251</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7529,16 +7539,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>S. K. Dankwah</t>
+          <t>I. Kwofie</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -7548,7 +7558,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7557,7 +7567,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M111" t="n">
         <v>1</v>
@@ -7567,7 +7577,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>EL100-A,EL100-B</t>
+          <t>EL200-A,EL200-B</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -7582,12 +7592,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EL 251</t>
+          <t>EL 261</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EL 251</t>
+          <t>EL 261</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7601,11 +7611,11 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>I. Kwofie</t>
+          <t>ANNAN</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -7627,7 +7637,7 @@
         <v>2</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -7649,12 +7659,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EL 261</t>
+          <t>EL 265</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EL 261</t>
+          <t>EL 265</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7668,11 +7678,11 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ANNAN</t>
+          <t>D. ARHINFUL</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -7682,7 +7692,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7694,7 +7704,7 @@
         <v>2</v>
       </c>
       <c r="M113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
@@ -7704,11 +7714,7 @@
           <t>EL200-A,EL200-B</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
@@ -7739,10 +7745,10 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -7779,12 +7785,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EL 265</t>
+          <t>EL 267</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EL 265</t>
+          <t>EL 267</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7798,14 +7804,14 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>D. ARHINFUL</t>
+          <t>KOMOLAFE</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -7842,12 +7848,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EL 267</t>
+          <t>EL 271</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EL 267</t>
+          <t>EL 271</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7861,7 +7867,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KOMOLAFE</t>
+          <t>AKORLI</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -7905,12 +7911,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EL 271</t>
+          <t>EL 273</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EL 271</t>
+          <t>EL 273</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7924,7 +7930,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AKORLI</t>
+          <t>Dr G. Owusu</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -7968,12 +7974,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EL 273</t>
+          <t>EL 275</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EL 273</t>
+          <t>EL 275</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7987,7 +7993,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dr G. Owusu</t>
+          <t>I. K. Prah</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -8031,12 +8037,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EL 275</t>
+          <t>EL 277</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EL 275</t>
+          <t>EL 277</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8050,11 +8056,11 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>I. K. Prah</t>
+          <t>AKORLI</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -8076,7 +8082,7 @@
         <v>2</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -8094,12 +8100,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EL 277</t>
+          <t>EL 361</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EL 277</t>
+          <t>EL 361</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8108,16 +8114,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AKORLI</t>
+          <t>ANAFO</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -8136,20 +8142,24 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>EL200-A,EL200-B</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr"/>
+          <t>EL300-A,EL300-B</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
@@ -8157,12 +8167,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EL 361</t>
+          <t>EL 363</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EL 361</t>
+          <t>EL 363</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8176,11 +8186,11 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ANAFO</t>
+          <t>NTI</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -8199,7 +8209,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121" t="n">
         <v>1</v>
@@ -8212,11 +8222,7 @@
           <t>EL300-A,EL300-B</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
@@ -8224,12 +8230,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EL 363</t>
+          <t>EL 365</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EL 363</t>
+          <t>EL 365</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8243,7 +8249,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NTI</t>
+          <t>Dr I. Ofori</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -8287,12 +8293,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EL 365</t>
+          <t>EL 367</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EL 365</t>
+          <t>EL 367</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8306,7 +8312,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dr I. Ofori</t>
+          <t>AMPOMAH</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -8350,12 +8356,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EL 367</t>
+          <t>EL 369</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EL 367</t>
+          <t>EL 369</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8369,11 +8375,11 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AMPOMAH</t>
+          <t>MUMUNI</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -8395,7 +8401,7 @@
         <v>2</v>
       </c>
       <c r="M124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -8413,12 +8419,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EL 369</t>
+          <t>EL 371</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EL 369</t>
+          <t>EL 371</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8432,11 +8438,11 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MUMUNI</t>
+          <t>S. K. Dankwah</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -8458,7 +8464,7 @@
         <v>2</v>
       </c>
       <c r="M125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N125" t="n">
         <v>0</v>
@@ -8476,12 +8482,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EL 371</t>
+          <t>EL 375</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EL 371</t>
+          <t>EL 375</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8495,7 +8501,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>S. K. Dankwah</t>
+          <t>AKORLI</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -8539,12 +8545,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EL 375</t>
+          <t>EL 377</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EL 375</t>
+          <t>EL 377</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8558,7 +8564,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AKORLI</t>
+          <t>I. K. Prah</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -8602,12 +8608,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EL 377</t>
+          <t>EL 451</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EL 377</t>
+          <t>EL 451</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8616,16 +8622,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>I. K. Prah</t>
+          <t>S. K. Dankwah</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -8644,7 +8650,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
@@ -8654,10 +8660,14 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>EL300-A,EL300-B</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr"/>
+          <t>EL400-A,EL400-B</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
@@ -8665,12 +8675,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EL 451</t>
+          <t>EL 459</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EL 451</t>
+          <t>EL 459</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8684,11 +8694,11 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>S. K. Dankwah</t>
+          <t>R. K. Amoah</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -8707,7 +8717,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M129" t="n">
         <v>1</v>
@@ -8720,11 +8730,7 @@
           <t>EL400-A,EL400-B</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
@@ -8732,12 +8738,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EL 459</t>
+          <t>EL 463</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EL 459</t>
+          <t>EL 463</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8751,7 +8757,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>R. K. Amoah</t>
+          <t>MUMUNI</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -8795,12 +8801,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EL 463</t>
+          <t>EL 465</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EL 463</t>
+          <t>EL 465</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8814,7 +8820,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MUMUNI</t>
+          <t>Dr E. M. Martey</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -8881,10 +8887,10 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -8921,12 +8927,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EL 465</t>
+          <t>EL 467</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EL 465</t>
+          <t>EL 467</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8940,14 +8946,14 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dr E. M. Martey</t>
+          <t>R. K. Amoah</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -8984,12 +8990,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EL 467</t>
+          <t>EL 471</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EL 467</t>
+          <t>EL 471</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9047,12 +9053,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EL 471</t>
+          <t>EL 473</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EL 471</t>
+          <t>EL 473</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9066,11 +9072,11 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>R. K. Amoah</t>
+          <t>ADJARDJA</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -9089,7 +9095,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M135" t="n">
         <v>1</v>
@@ -9102,7 +9108,11 @@
           <t>EL400-A,EL400-B</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr"/>
@@ -9110,12 +9120,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EL 473</t>
+          <t>EL 475</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EL 473</t>
+          <t>EL 475</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9129,11 +9139,11 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ADJARDJA</t>
+          <t>I. K. Prah</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -9152,7 +9162,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M136" t="n">
         <v>1</v>
@@ -9165,11 +9175,7 @@
           <t>EL400-A,EL400-B</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr"/>
@@ -9177,30 +9183,30 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EL 475</t>
+          <t>ES 141</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EL 475</t>
+          <t>ES 141</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>I. K. Prah</t>
+          <t>ADZAKOR</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -9219,7 +9225,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
         <v>1</v>
@@ -9229,10 +9235,14 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>EL400-A,EL400-B</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr"/>
+          <t>ES100-A,ES100-B</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
@@ -9240,12 +9250,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ES 141</t>
+          <t>ES 151</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ES 141</t>
+          <t>ES 151</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9259,11 +9269,11 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ADZAKOR</t>
+          <t>S. K. Dankwah</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -9282,10 +9292,10 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -9295,11 +9305,7 @@
           <t>ES100-A,ES100-B</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
@@ -9307,12 +9313,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ES 151</t>
+          <t>ES 153</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ES 151</t>
+          <t>ES 153</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9326,11 +9332,11 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>S. K. Dankwah</t>
+          <t>NTI</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -9352,7 +9358,7 @@
         <v>2</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -9370,12 +9376,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ES 153</t>
+          <t>ES 155</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ES 153</t>
+          <t>ES 155</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9389,11 +9395,11 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NTI</t>
+          <t>E. Adu Kyeremeh</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -9415,7 +9421,7 @@
         <v>2</v>
       </c>
       <c r="M140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -9433,12 +9439,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ES 155</t>
+          <t>ES 157</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ES 155</t>
+          <t>ES 157</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9452,11 +9458,11 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>E. Adu Kyeremeh</t>
+          <t>TORTOR</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -9475,10 +9481,10 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -9488,7 +9494,11 @@
           <t>ES100-A,ES100-B</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
@@ -9496,12 +9506,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ES 157</t>
+          <t>ES 159</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ES 157</t>
+          <t>ES 159</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9515,11 +9525,11 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>TORTOR</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -9538,7 +9548,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M142" t="n">
         <v>1</v>
@@ -9551,11 +9561,7 @@
           <t>ES100-A,ES100-B</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
@@ -9563,12 +9569,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ES 159</t>
+          <t>ES 161</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ES 159</t>
+          <t>ES 161</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9582,7 +9588,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>SEIDU</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -9626,12 +9632,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ES 161</t>
+          <t>ES 167</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ES 161</t>
+          <t>ES 167</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9645,7 +9651,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SEIDU</t>
+          <t>S. K. Yormesor</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -9689,12 +9695,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ES 167</t>
+          <t>ES 171</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ES 167</t>
+          <t>ES 171</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9708,7 +9714,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>S. K. Yormesor</t>
+          <t>ASHUN</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -9722,7 +9728,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9744,7 +9750,11 @@
           <t>ES100-A,ES100-B</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
@@ -9752,12 +9762,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ES 171</t>
+          <t>ES 251</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ES 171</t>
+          <t>ES 251</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9766,16 +9776,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ASHUN</t>
+          <t>I. Kwofie</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -9797,14 +9807,14 @@
         <v>2</v>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N146" t="n">
         <v>0</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>ES100-A,ES100-B</t>
+          <t>ES200-A,ES200-B</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -9819,12 +9829,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ES 251</t>
+          <t>ES 255</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ES 251</t>
+          <t>ES 255</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9838,11 +9848,11 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>I. Kwofie</t>
+          <t>D. ARHINFUL</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -9852,7 +9862,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9861,10 +9871,10 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -9886,12 +9896,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ES 255</t>
+          <t>ES 259</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ES 255</t>
+          <t>ES 259</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9905,7 +9915,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>D. ARHINFUL</t>
+          <t>ADOMAKO-ANSAH</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -9919,7 +9929,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9953,12 +9963,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ES 259</t>
+          <t>ES 271</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ES 259</t>
+          <t>ES 271</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9972,11 +9982,11 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>ADOMAKO-ANSAH</t>
+          <t>ASHUN</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -9995,7 +10005,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M149" t="n">
         <v>1</v>
@@ -10020,12 +10030,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ES 271</t>
+          <t>ES 273</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ES 271</t>
+          <t>ES 273</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10039,7 +10049,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ASHUN</t>
+          <t>ATTATSI</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -10087,12 +10097,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ES 273</t>
+          <t>ES 275</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ES 273</t>
+          <t>ES 275</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10120,7 +10130,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10142,11 +10152,7 @@
           <t>ES200-A,ES200-B</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
@@ -10154,12 +10160,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ES 275</t>
+          <t>ES 277</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ES 275</t>
+          <t>ES 277</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10173,11 +10179,11 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ATTATSI</t>
+          <t>Dr I. Ofori</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -10187,7 +10193,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10196,7 +10202,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
@@ -10209,7 +10215,11 @@
           <t>ES200-A,ES200-B</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
@@ -10217,12 +10227,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ES 277</t>
+          <t>ES 279</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ES 277</t>
+          <t>ES 279</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10240,7 +10250,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -10250,7 +10260,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10259,7 +10269,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M153" t="n">
         <v>1</v>
@@ -10272,11 +10282,7 @@
           <t>ES200-A,ES200-B</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
@@ -10284,12 +10290,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ES 279</t>
+          <t>ES 351</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ES 279</t>
+          <t>ES 351</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10298,12 +10304,12 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dr I. Ofori</t>
+          <t>Dr A. A. Amponsah</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -10336,7 +10342,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>ES200-A,ES200-B</t>
+          <t>ES300-A,ES300-B</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -10347,12 +10353,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ES 351</t>
+          <t>ES 361</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ES 351</t>
+          <t>ES 361</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10366,11 +10372,11 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dr A. A. Amponsah</t>
+          <t>ANAFO</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -10392,7 +10398,7 @@
         <v>2</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -10410,12 +10416,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ES 361</t>
+          <t>ES 371</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ES 361</t>
+          <t>ES 371</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10429,11 +10435,11 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ANAFO</t>
+          <t>ASHUN</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -10455,7 +10461,7 @@
         <v>2</v>
       </c>
       <c r="M156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N156" t="n">
         <v>0</v>
@@ -10473,12 +10479,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ES 371</t>
+          <t>ES 373</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ES 371</t>
+          <t>ES 373</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10492,7 +10498,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ASHUN</t>
+          <t>Dr I. Ofori</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -10536,12 +10542,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ES 373</t>
+          <t>ES 375</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ES 373</t>
+          <t>ES 375</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10555,11 +10561,11 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dr I. Ofori</t>
+          <t>ATTATSI</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -10578,7 +10584,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M158" t="n">
         <v>1</v>
@@ -10591,7 +10597,11 @@
           <t>ES300-A,ES300-B</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr"/>
@@ -10599,12 +10609,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ES 375</t>
+          <t>ES 377</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ES 375</t>
+          <t>ES 377</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10622,7 +10632,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -10641,7 +10651,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M159" t="n">
         <v>1</v>
@@ -10654,11 +10664,7 @@
           <t>ES300-A,ES300-B</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr"/>
@@ -10666,12 +10672,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ES 377</t>
+          <t>ES 379</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ES 377</t>
+          <t>ES 379</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10685,7 +10691,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ATTATSI</t>
+          <t>ASHUN</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -10699,7 +10705,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10721,7 +10727,11 @@
           <t>ES300-A,ES300-B</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr"/>
@@ -10729,12 +10739,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ES 379</t>
+          <t>ES 381</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ES 379</t>
+          <t>ES 381</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10748,7 +10758,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ASHUN</t>
+          <t>Dr I. Ofori</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -10762,7 +10772,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10784,11 +10794,7 @@
           <t>ES300-A,ES300-B</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
@@ -10796,12 +10802,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ES 381</t>
+          <t>ES 451</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ES 381</t>
+          <t>ES 451</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10810,7 +10816,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
@@ -10848,7 +10854,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>ES300-A,ES300-B</t>
+          <t>ES400-A,ES400-B</t>
         </is>
       </c>
       <c r="P162" t="inlineStr"/>
@@ -10859,12 +10865,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ES 451</t>
+          <t>ES 455</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ES 451</t>
+          <t>ES 455</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10878,14 +10884,14 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dr I. Ofori</t>
+          <t>M. B. Poku</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -10903,9 +10909,7 @@
       <c r="L163" t="n">
         <v>2</v>
       </c>
-      <c r="M163" t="n">
-        <v>1</v>
-      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="n">
         <v>0</v>
       </c>
@@ -10922,12 +10926,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ES 455</t>
+          <t>ES 459</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ES 455</t>
+          <t>ES 459</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10941,14 +10945,14 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M. B. Poku</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -10970,11 +10974,7 @@
       <c r="N164" t="n">
         <v>0</v>
       </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>ES400-A,ES400-B</t>
-        </is>
-      </c>
+      <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -11040,17 +11040,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ES 459</t>
+          <t>GM 459</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ES 459</t>
+          <t>GM 459</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -11063,10 +11063,10 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -11120,10 +11120,10 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -11154,17 +11154,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GM 459</t>
+          <t>ES 467</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GM 459</t>
+          <t>ES 467</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -11173,14 +11173,14 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>R. K. Amoah</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -11192,17 +11192,23 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
       <c r="N168" t="n">
         <v>0</v>
       </c>
-      <c r="O168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>ES400-A,ES400-B</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
@@ -11211,12 +11217,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ES 467</t>
+          <t>ES 471</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ES 467</t>
+          <t>ES 471</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11230,7 +11236,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>R. K. Amoah</t>
+          <t>ASHUN</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -11274,12 +11280,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ES 471</t>
+          <t>ES 473</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ES 471</t>
+          <t>ES 473</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11293,7 +11299,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ASHUN</t>
+          <t>Dr I. Ofori</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -11307,7 +11313,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11329,7 +11335,11 @@
           <t>ES400-A,ES400-B</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
@@ -11337,30 +11347,30 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ES 473</t>
+          <t>GL 141</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ES 473</t>
+          <t>GL 141</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dr I. Ofori</t>
+          <t>ADZAKOR</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -11370,7 +11380,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11379,7 +11389,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M171" t="n">
         <v>1</v>
@@ -11389,7 +11399,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>ES400-A,ES400-B</t>
+          <t>GL100-A,GL100-B</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -11404,12 +11414,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GL 141</t>
+          <t>GL 151</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GL 141</t>
+          <t>GL 151</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11423,11 +11433,11 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ADZAKOR</t>
+          <t>Dr G. Owusu</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -11446,7 +11456,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
         <v>1</v>
@@ -11459,11 +11469,7 @@
           <t>GL100-A,GL100-B</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
@@ -11471,12 +11477,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GL 151</t>
+          <t>GL 153</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GL 151</t>
+          <t>GL 153</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11490,11 +11496,11 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dr G. Owusu</t>
+          <t>NTI</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -11516,7 +11522,7 @@
         <v>2</v>
       </c>
       <c r="M173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N173" t="n">
         <v>0</v>
@@ -11534,12 +11540,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GL 153</t>
+          <t>GL 155</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GL 153</t>
+          <t>GL 155</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11553,11 +11559,11 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NTI</t>
+          <t>A. O. Mohammed</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -11576,10 +11582,10 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N174" t="n">
         <v>0</v>
@@ -11589,7 +11595,11 @@
           <t>GL100-A,GL100-B</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
@@ -11597,12 +11607,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GL 155</t>
+          <t>GL 157</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GL 155</t>
+          <t>GL 157</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11616,7 +11626,7 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>A. O. Mohammed</t>
+          <t>TORTOR</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -11664,17 +11674,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GL 157</t>
+          <t>MF 157</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GL 157</t>
+          <t>MF 157</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>MF</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -11687,7 +11697,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -11697,7 +11707,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11706,7 +11716,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M176" t="n">
         <v>1</v>
@@ -11716,7 +11726,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>GL100-A,GL100-B</t>
+          <t>MF100-A</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -11731,17 +11741,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MF 157</t>
+          <t>GL 159</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MF 157</t>
+          <t>GL 159</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -11750,7 +11760,7 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TORTOR</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -11764,7 +11774,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11783,14 +11793,10 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>MF100-A</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>GL100-A,GL100-B</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
@@ -11798,12 +11804,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GL 159</t>
+          <t>GL 167</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GL 159</t>
+          <t>GL 167</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11817,7 +11823,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>NANOR</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -11861,12 +11867,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GL 167</t>
+          <t>GL 171</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GL 167</t>
+          <t>GL 171</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11880,11 +11886,11 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>NANOR</t>
+          <t>SEIDU</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -11906,7 +11912,7 @@
         <v>2</v>
       </c>
       <c r="M179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N179" t="n">
         <v>0</v>
@@ -11924,12 +11930,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GL 171</t>
+          <t>GL 251</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GL 171</t>
+          <t>GL 251</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11938,16 +11944,16 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SEIDU</t>
+          <t>I. Kwofie</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -11957,7 +11963,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11969,17 +11975,21 @@
         <v>2</v>
       </c>
       <c r="M180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N180" t="n">
         <v>0</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>GL100-A,GL100-B</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr"/>
+          <t>GL200-A,GL200-B</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
@@ -11987,12 +11997,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GL 251</t>
+          <t>GL 255</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GL 251</t>
+          <t>GL 255</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12006,7 +12016,7 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>I. Kwofie</t>
+          <t>D. ARHINFUL</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -12020,7 +12030,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12029,10 +12039,10 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N181" t="n">
         <v>0</v>
@@ -12042,11 +12052,7 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
@@ -12054,12 +12060,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GL 255</t>
+          <t>GL 261</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GL 255</t>
+          <t>GL 261</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12073,7 +12079,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>D. ARHINFUL</t>
+          <t>YALLEY</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -12087,7 +12093,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12096,10 +12102,10 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N182" t="n">
         <v>0</v>
@@ -12109,7 +12115,11 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
@@ -12117,12 +12127,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GL 261</t>
+          <t>GL 271</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GL 261</t>
+          <t>GL 271</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12136,7 +12146,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>YALLEY</t>
+          <t>E. Benyarku</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -12184,12 +12194,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>GL 271</t>
+          <t>GL 273</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GL 271</t>
+          <t>GL 273</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -12203,11 +12213,11 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>E. Benyarku</t>
+          <t>Dr S. Sebbeh-Newton</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -12217,7 +12227,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12229,7 +12239,7 @@
         <v>2</v>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N184" t="n">
         <v>0</v>
@@ -12239,11 +12249,7 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
@@ -12251,12 +12257,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GL 273</t>
+          <t>GL 275</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GL 273</t>
+          <t>GL 275</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -12270,11 +12276,11 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dr S. Sebbeh-Newton</t>
+          <t>G.M. TETTEH</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -12284,7 +12290,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12296,7 +12302,7 @@
         <v>2</v>
       </c>
       <c r="M185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N185" t="n">
         <v>0</v>
@@ -12306,7 +12312,11 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
@@ -12314,12 +12324,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>GL 275</t>
+          <t>GL 277</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GL 275</t>
+          <t>GL 277</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -12333,11 +12343,11 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>G.M. TETTEH</t>
+          <t>E. Benyarku</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -12347,7 +12357,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12359,7 +12369,7 @@
         <v>2</v>
       </c>
       <c r="M186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N186" t="n">
         <v>0</v>
@@ -12369,11 +12379,7 @@
           <t>GL200-A,GL200-B</t>
         </is>
       </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
@@ -12381,12 +12387,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>GL 277</t>
+          <t>GL 279</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GL 277</t>
+          <t>GL 279</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -12400,11 +12406,11 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>E. Benyarku</t>
+          <t>E. Annan-Boah</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -12426,7 +12432,7 @@
         <v>2</v>
       </c>
       <c r="M187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N187" t="n">
         <v>0</v>
@@ -12444,12 +12450,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GL 279</t>
+          <t>GL 351</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>GL 279</t>
+          <t>GL 351</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12458,16 +12464,16 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>E. Annan-Boah</t>
+          <t>E. Obu</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -12489,17 +12495,21 @@
         <v>2</v>
       </c>
       <c r="M188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N188" t="n">
         <v>0</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>GL200-A,GL200-B</t>
-        </is>
-      </c>
-      <c r="P188" t="inlineStr"/>
+          <t>GL300-A,GL300-B</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
@@ -12507,12 +12517,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GL 351</t>
+          <t>GL 353</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GL 351</t>
+          <t>GL 353</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12526,7 +12536,7 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>E. Obu</t>
+          <t>TABASE</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -12574,12 +12584,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GL 353</t>
+          <t>GL 357</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GL 353</t>
+          <t>GL 357</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12593,11 +12603,11 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TABASE</t>
+          <t>Dr S. Sebbeh-Newton</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -12619,7 +12629,7 @@
         <v>2</v>
       </c>
       <c r="M190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N190" t="n">
         <v>0</v>
@@ -12629,11 +12639,7 @@
           <t>GL300-A,GL300-B</t>
         </is>
       </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
@@ -12641,12 +12647,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>GL 357</t>
+          <t>GL 361</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GL 357</t>
+          <t>GL 361</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12660,7 +12666,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dr S. Sebbeh-Newton</t>
+          <t>ANAFO</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -12704,12 +12710,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GL 361</t>
+          <t>GL 371</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>GL 361</t>
+          <t>GL 371</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12723,11 +12729,11 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ANAFO</t>
+          <t>E. Benyarku</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -12749,7 +12755,7 @@
         <v>2</v>
       </c>
       <c r="M192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N192" t="n">
         <v>0</v>
@@ -12759,7 +12765,11 @@
           <t>GL300-A,GL300-B</t>
         </is>
       </c>
-      <c r="P192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
@@ -12767,12 +12777,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GL 371</t>
+          <t>GL 373</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>GL 371</t>
+          <t>GL 373</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12786,7 +12796,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>E. Benyarku</t>
+          <t>Dr S. Sebbeh-Newton</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -12857,10 +12867,10 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
@@ -12872,14 +12882,14 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L194" t="n">
         <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N194" t="n">
         <v>0</v>
@@ -12889,11 +12899,7 @@
           <t>GL300-A,GL300-B</t>
         </is>
       </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
@@ -12901,12 +12907,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GL 373</t>
+          <t>GL 375</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GL 373</t>
+          <t>GL 375</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12920,14 +12926,14 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dr S. Sebbeh-Newton</t>
+          <t>SEIDU</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H195" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -12939,14 +12945,14 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N195" t="n">
         <v>0</v>
@@ -12956,7 +12962,11 @@
           <t>GL300-A,GL300-B</t>
         </is>
       </c>
-      <c r="P195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
@@ -12964,12 +12974,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GL 375</t>
+          <t>GL 377</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GL 375</t>
+          <t>GL 377</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13031,12 +13041,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GL 377</t>
+          <t>GL 451</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GL 377</t>
+          <t>GL 451</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -13045,7 +13055,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
@@ -13064,7 +13074,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13083,7 +13093,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>GL300-A,GL300-B</t>
+          <t>GL400-A,GL400-B</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -13098,12 +13108,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GL 451</t>
+          <t>GL 453</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GL 451</t>
+          <t>GL 453</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -13117,7 +13127,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SEIDU</t>
+          <t>S. AFFUL</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -13142,9 +13152,7 @@
       <c r="L198" t="n">
         <v>2</v>
       </c>
-      <c r="M198" t="n">
-        <v>1</v>
-      </c>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="n">
         <v>0</v>
       </c>
@@ -13165,12 +13173,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GL 453</t>
+          <t>GL 455</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GL 453</t>
+          <t>GL 455</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -13184,11 +13192,11 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>S. AFFUL</t>
+          <t>M. B. Poku</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -13213,11 +13221,7 @@
       <c r="N199" t="n">
         <v>0</v>
       </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>GL400-A,GL400-B</t>
-        </is>
-      </c>
+      <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>no</t>
@@ -13253,17 +13257,17 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13279,11 +13283,7 @@
         <v>0</v>
       </c>
       <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
@@ -13291,12 +13291,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>GL 455</t>
+          <t>GL 459</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GL 455</t>
+          <t>GL 459</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -13310,21 +13310,21 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>M. B. Poku</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13335,12 +13335,22 @@
       <c r="L201" t="n">
         <v>2</v>
       </c>
-      <c r="M201" t="inlineStr"/>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
       <c r="N201" t="n">
         <v>0</v>
       </c>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>GL400-A,GL400-B</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
@@ -13348,12 +13358,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>GL 459</t>
+          <t>GL 471</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GL 459</t>
+          <t>GL 471</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -13367,11 +13377,11 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>E. Benyarku</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -13381,7 +13391,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13390,7 +13400,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M202" t="n">
         <v>1</v>
@@ -13415,12 +13425,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>GL 471</t>
+          <t>GL 473</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GL 471</t>
+          <t>GL 473</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -13434,11 +13444,11 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>E. Benyarku</t>
+          <t>E. N. Asare</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -13448,7 +13458,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13457,7 +13467,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M203" t="n">
         <v>1</v>
@@ -13505,22 +13515,22 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
       <c r="L204" t="n">
@@ -13549,33 +13559,33 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GL 473</t>
+          <t>GM 141</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GL 473</t>
+          <t>GM 141</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>E. N. Asare</t>
+          <t>ADZAKOR</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -13587,11 +13597,11 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M205" t="n">
         <v>1</v>
@@ -13601,7 +13611,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>GL400-A,GL400-B</t>
+          <t>GM100-A,GM100-B</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -13616,12 +13626,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GM 141</t>
+          <t>GM 151</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>GM 141</t>
+          <t>GM 151</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13635,11 +13645,11 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ADZAKOR</t>
+          <t>I. K. Prah</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -13658,7 +13668,7 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M206" t="n">
         <v>1</v>
@@ -13683,12 +13693,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GM 151</t>
+          <t>GM 153</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GM 151</t>
+          <t>GM 153</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13702,7 +13712,7 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>I. K. Prah</t>
+          <t>NTI</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -13750,12 +13760,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GM 153</t>
+          <t>GM 155</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GM 153</t>
+          <t>GM 155</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13769,7 +13779,7 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>NTI</t>
+          <t>A. O. Mohammed</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -13817,12 +13827,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GM 155</t>
+          <t>GM 157</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GM 155</t>
+          <t>GM 157</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13836,11 +13846,11 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>A. O. Mohammed</t>
+          <t>TORTOR</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -13859,7 +13869,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M209" t="n">
         <v>1</v>
@@ -13884,17 +13894,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>GM 157</t>
+          <t>TM 157</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GM 157</t>
+          <t>TM 157</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -13907,7 +13917,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -13917,7 +13927,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -13926,7 +13936,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M210" t="n">
         <v>1</v>
@@ -13936,7 +13946,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>GM100-A,GM100-B</t>
+          <t>TM100-A</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -13951,17 +13961,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TM 157</t>
+          <t>GM 159</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TM 157</t>
+          <t>GM 159</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -13970,7 +13980,7 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>TORTOR</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -14003,7 +14013,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>TM100-A</t>
+          <t>GM100-A,GM100-B</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -14018,12 +14028,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>GM 159</t>
+          <t>GM 161</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GM 159</t>
+          <t>GM 161</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14037,7 +14047,7 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>Dr S. Sebbeh-Newton</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -14051,7 +14061,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14085,12 +14095,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GM 161</t>
+          <t>GM 167</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GM 161</t>
+          <t>GM 167</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -14104,7 +14114,7 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dr S. Sebbeh-Newton</t>
+          <t>S. K. Yormesor</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -14152,12 +14162,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>GM 167</t>
+          <t>GM 171</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>GM 167</t>
+          <t>GM 171</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -14171,7 +14181,7 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>S. K. Yormesor</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -14219,12 +14229,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>GM 171</t>
+          <t>GM 251</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>GM 171</t>
+          <t>GM 251</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -14233,12 +14243,12 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>I. Kwofie</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -14252,7 +14262,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14271,7 +14281,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>GM100-A,GM100-B</t>
+          <t>GM200-A,GM200-B</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -14286,12 +14296,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GM 251</t>
+          <t>GM 255</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>GM 251</t>
+          <t>GM 255</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -14305,11 +14315,11 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>I. Kwofie</t>
+          <t>D. ARHINFUL</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -14319,7 +14329,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14328,7 +14338,7 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
         <v>1</v>
@@ -14353,12 +14363,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>GM 255</t>
+          <t>GM 261</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>GM 255</t>
+          <t>GM 261</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -14372,11 +14382,11 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>D. ARHINFUL</t>
+          <t>HAWARD-FERGUSON</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -14386,7 +14396,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14395,7 +14405,7 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M217" t="n">
         <v>1</v>
@@ -14420,12 +14430,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GM 261</t>
+          <t>GM 271</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>GM 261</t>
+          <t>GM 271</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -14439,7 +14449,7 @@
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>HAWARD-FERGUSON</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -14487,12 +14497,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>GM 271</t>
+          <t>GM 273</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>GM 271</t>
+          <t>GM 273</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -14506,11 +14516,11 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>M. B. Poku</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -14520,7 +14530,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -14532,7 +14542,7 @@
         <v>2</v>
       </c>
       <c r="M219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N219" t="n">
         <v>0</v>
@@ -14542,11 +14552,7 @@
           <t>GM200-A,GM200-B</t>
         </is>
       </c>
-      <c r="P219" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr"/>
@@ -14554,12 +14560,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GM 273</t>
+          <t>GM 275</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>GM 273</t>
+          <t>GM 275</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -14573,11 +14579,11 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>M. B. Poku</t>
+          <t>TAGOE</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -14599,7 +14605,7 @@
         <v>2</v>
       </c>
       <c r="M220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N220" t="n">
         <v>0</v>
@@ -14609,7 +14615,11 @@
           <t>GM200-A,GM200-B</t>
         </is>
       </c>
-      <c r="P220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
@@ -14617,12 +14627,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>GM 275</t>
+          <t>GM 277</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>GM 275</t>
+          <t>GM 277</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -14636,7 +14646,7 @@
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>TAGOE</t>
+          <t>TABASE</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -14684,12 +14694,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>GM 277</t>
+          <t>GM 285</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GM 277</t>
+          <t>GM 285</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14703,7 +14713,7 @@
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>TABASE</t>
+          <t>HAWARD-FERGUSON</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -14717,7 +14727,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -14751,12 +14761,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GM 285</t>
+          <t>GM 351</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>GM 285</t>
+          <t>GM 351</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14765,12 +14775,12 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>HAWARD-FERGUSON</t>
+          <t>Dr A. A. Amponsah</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -14784,7 +14794,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -14803,7 +14813,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>GM200-A,GM200-B</t>
+          <t>GM300-A,GM300-B</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -14818,12 +14828,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>GM 351</t>
+          <t>GM 353</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>GM 351</t>
+          <t>GM 353</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14837,7 +14847,7 @@
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Dr A. A. Amponsah</t>
+          <t>AKYEN</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -14908,10 +14918,10 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
@@ -14952,12 +14962,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>GM 353</t>
+          <t>GM 361</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>GM 353</t>
+          <t>GM 361</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14971,14 +14981,14 @@
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>AKYEN</t>
+          <t>ANAFO</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -14997,7 +15007,7 @@
         <v>2</v>
       </c>
       <c r="M226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N226" t="n">
         <v>0</v>
@@ -15007,11 +15017,7 @@
           <t>GM300-A,GM300-B</t>
         </is>
       </c>
-      <c r="P226" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
@@ -15019,12 +15025,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GM 361</t>
+          <t>GM 365</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>GM 361</t>
+          <t>GM 365</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -15038,11 +15044,11 @@
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>ANAFO</t>
+          <t>ATTAFUAH</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -15052,7 +15058,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15064,7 +15070,7 @@
         <v>2</v>
       </c>
       <c r="M227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N227" t="n">
         <v>0</v>
@@ -15074,7 +15080,11 @@
           <t>GM300-A,GM300-B</t>
         </is>
       </c>
-      <c r="P227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr"/>
@@ -15082,12 +15092,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>GM 365</t>
+          <t>GM 373</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>GM 365</t>
+          <t>GM 373</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -15101,7 +15111,7 @@
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>ATTAFUAH</t>
+          <t>ZIGGAH</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -15149,12 +15159,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>GM 373</t>
+          <t>GM 375</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>GM 373</t>
+          <t>GM 375</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15168,7 +15178,7 @@
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>ZIGGAH</t>
+          <t>E. Annan-Boah</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -15182,7 +15192,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15239,10 +15249,10 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -15254,14 +15264,14 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L230" t="n">
         <v>2</v>
       </c>
       <c r="M230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N230" t="n">
         <v>0</v>
@@ -15271,11 +15281,7 @@
           <t>GM300-A,GM300-B</t>
         </is>
       </c>
-      <c r="P230" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
@@ -15283,12 +15289,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GM 375</t>
+          <t>GM 377</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>GM 375</t>
+          <t>GM 377</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -15302,14 +15308,14 @@
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>E. Annan-Boah</t>
+          <t>Dr T. Kwantwi</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H231" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -15321,14 +15327,14 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L231" t="n">
         <v>2</v>
       </c>
       <c r="M231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N231" t="n">
         <v>0</v>
@@ -15338,7 +15344,11 @@
           <t>GM300-A,GM300-B</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
@@ -15346,12 +15356,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GM 377</t>
+          <t>GM 379</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>GM 377</t>
+          <t>GM 379</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -15365,7 +15375,7 @@
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Dr T. Kwantwi</t>
+          <t>E. Annan-Boah</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -15413,12 +15423,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GM 379</t>
+          <t>GM 451</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>GM 379</t>
+          <t>GM 451</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -15427,16 +15437,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>E. Annan-Boah</t>
+          <t>TAGOE</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -15455,7 +15465,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M233" t="n">
         <v>1</v>
@@ -15465,7 +15475,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>GM300-A,GM300-B</t>
+          <t>GM400-A,GM400-B</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -15480,12 +15490,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>GM 451</t>
+          <t>GM 453</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>GM 451</t>
+          <t>GM 453</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -15499,11 +15509,11 @@
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TAGOE</t>
+          <t>S. AFFUL</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -15513,7 +15523,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -15522,19 +15532,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1</v>
-      </c>
-      <c r="M234" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M234" t="inlineStr"/>
       <c r="N234" t="n">
         <v>0</v>
       </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>GM400-A,GM400-B</t>
-        </is>
-      </c>
+      <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>no</t>
@@ -15547,17 +15551,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>GM 453</t>
+          <t>ES 453</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>GM 453</t>
+          <t>ES 453</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -15608,17 +15612,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ES 453</t>
+          <t>GM 471</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ES 453</t>
+          <t>GM 471</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -15627,11 +15631,11 @@
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>S. AFFUL</t>
+          <t>YALLEY</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -15650,13 +15654,19 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2</v>
-      </c>
-      <c r="M236" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M236" t="n">
+        <v>1</v>
+      </c>
       <c r="N236" t="n">
         <v>0</v>
       </c>
-      <c r="O236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>GM400-A,GM400-B</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>no</t>
@@ -15669,12 +15679,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>GM 471</t>
+          <t>GM 473</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>GM 471</t>
+          <t>GM 473</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -15688,11 +15698,11 @@
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>YALLEY</t>
+          <t>M. B. Poku</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -15702,7 +15712,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -15711,10 +15721,10 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N237" t="n">
         <v>0</v>
@@ -15724,11 +15734,7 @@
           <t>GM400-A,GM400-B</t>
         </is>
       </c>
-      <c r="P237" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
@@ -15736,12 +15742,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GM 473</t>
+          <t>GM 475</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>GM 473</t>
+          <t>GM 475</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -15755,11 +15761,11 @@
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>M. B. Poku</t>
+          <t>TAGOE</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -15781,7 +15787,7 @@
         <v>2</v>
       </c>
       <c r="M238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N238" t="n">
         <v>0</v>
@@ -15791,7 +15797,11 @@
           <t>GM400-A,GM400-B</t>
         </is>
       </c>
-      <c r="P238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
@@ -15822,10 +15832,10 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -15837,14 +15847,14 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L239" t="n">
         <v>2</v>
       </c>
       <c r="M239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N239" t="n">
         <v>0</v>
@@ -15854,11 +15864,7 @@
           <t>GM400-A,GM400-B</t>
         </is>
       </c>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P239" t="inlineStr"/>
       <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
@@ -15866,12 +15872,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>GM 475</t>
+          <t>GM 477</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>GM 475</t>
+          <t>GM 477</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15885,33 +15891,33 @@
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>TAGOE</t>
+          <t>E. N. Asare</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H240" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L240" t="n">
         <v>2</v>
       </c>
       <c r="M240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N240" t="n">
         <v>0</v>
@@ -15921,7 +15927,11 @@
           <t>GM400-A,GM400-B</t>
         </is>
       </c>
-      <c r="P240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
@@ -15929,17 +15939,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>GM 477</t>
+          <t>MA 451</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>GM 477</t>
+          <t>MA 451</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -15948,7 +15958,7 @@
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>E. N. Asare</t>
+          <t>Assoc Prof J. Acquah</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -15962,7 +15972,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -15981,14 +15991,10 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>GM400-A,GM400-B</t>
-        </is>
-      </c>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>MA400-A</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
@@ -15996,12 +16002,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MA 451</t>
+          <t>MA 471</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MA 451</t>
+          <t>MA 471</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -16019,7 +16025,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -16041,7 +16047,7 @@
         <v>2</v>
       </c>
       <c r="M242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N242" t="n">
         <v>0</v>
@@ -16059,12 +16065,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MA 471</t>
+          <t>MA 473</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MA 471</t>
+          <t>MA 473</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -16078,7 +16084,7 @@
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Assoc Prof J. Acquah</t>
+          <t>Owusu-Bempah</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -16122,12 +16128,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MA 473</t>
+          <t>MA 475</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>MA 473</t>
+          <t>MA 475</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -16141,7 +16147,7 @@
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Owusu-Bempah</t>
+          <t>NTI</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -16185,12 +16191,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MA 475</t>
+          <t>MA 477</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>MA 475</t>
+          <t>MA 477</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -16248,12 +16254,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>MA 477</t>
+          <t>MA 479</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MA 477</t>
+          <t>MA 479</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -16267,7 +16273,7 @@
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NTI</t>
+          <t>ANAFO</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -16311,12 +16317,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MA 479</t>
+          <t>MA 481</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>MA 479</t>
+          <t>MA 481</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -16330,11 +16336,11 @@
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>ANAFO</t>
+          <t>Assoc Prof J. Acquah</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -16356,7 +16362,7 @@
         <v>2</v>
       </c>
       <c r="M247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N247" t="n">
         <v>0</v>
@@ -16374,30 +16380,30 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MA 481</t>
+          <t>MC 141</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MA 481</t>
+          <t>MC 141</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Assoc Prof J. Acquah</t>
+          <t>ADZAKOR</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -16416,7 +16422,7 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M248" t="n">
         <v>1</v>
@@ -16426,10 +16432,14 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>MA400-A</t>
-        </is>
-      </c>
-      <c r="P248" t="inlineStr"/>
+          <t>MC100-A,MC100-B</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr"/>
@@ -16437,12 +16447,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MC 141</t>
+          <t>MC 151</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MC 141</t>
+          <t>MC 151</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -16456,11 +16466,11 @@
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>ADZAKOR</t>
+          <t>Dr G. Owusu</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -16479,10 +16489,10 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N249" t="n">
         <v>0</v>
@@ -16492,11 +16502,7 @@
           <t>MC100-A,MC100-B</t>
         </is>
       </c>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P249" t="inlineStr"/>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr"/>
@@ -16504,12 +16510,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MC 151</t>
+          <t>MC 155</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MC 151</t>
+          <t>MC 155</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -16523,7 +16529,7 @@
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Dr G. Owusu</t>
+          <t>A. O. Mohammed</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -16567,12 +16573,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MC 155</t>
+          <t>MC 157</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>MC 155</t>
+          <t>MC 157</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -16586,11 +16592,11 @@
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>A. O. Mohammed</t>
+          <t>E. ARHINFUL</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -16609,10 +16615,10 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N251" t="n">
         <v>0</v>
@@ -16622,7 +16628,11 @@
           <t>MC100-A,MC100-B</t>
         </is>
       </c>
-      <c r="P251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
@@ -16653,17 +16663,17 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -16672,7 +16682,7 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M252" t="n">
         <v>1</v>
@@ -16697,12 +16707,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MC 157</t>
+          <t>MC 159</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>MC 157</t>
+          <t>MC 159</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -16716,21 +16726,21 @@
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>E. ARHINFUL</t>
+          <t>Dr A. A. Amponsah</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -16787,10 +16797,10 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I254" t="n">
         <v>0</v>
@@ -16831,12 +16841,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MC 159</t>
+          <t>MC 163</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MC 159</t>
+          <t>MC 163</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16850,21 +16860,21 @@
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Dr A. A. Amponsah</t>
+          <t>E. Obu</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I255" t="n">
         <v>0</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -16921,17 +16931,17 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I256" t="n">
         <v>0</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -16965,12 +16975,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>MC 163</t>
+          <t>MC 169</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>MC 163</t>
+          <t>MC 169</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16984,14 +16994,14 @@
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>E. Obu</t>
+          <t>AMPOFI</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H257" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I257" t="n">
         <v>0</v>
@@ -17010,7 +17020,7 @@
         <v>2</v>
       </c>
       <c r="M257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N257" t="n">
         <v>0</v>
@@ -17020,11 +17030,7 @@
           <t>MC100-A,MC100-B</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P257" t="inlineStr"/>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr"/>
@@ -17032,12 +17038,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MC 169</t>
+          <t>MC 171</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MC 169</t>
+          <t>MC 171</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -17051,11 +17057,11 @@
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>AMPOFI</t>
+          <t>ODOOM</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -17074,10 +17080,10 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N258" t="n">
         <v>0</v>
@@ -17087,7 +17093,11 @@
           <t>MC100-A,MC100-B</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr"/>
@@ -17095,12 +17105,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>MC 171</t>
+          <t>MC 173</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>MC 171</t>
+          <t>MC 173</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -17114,11 +17124,11 @@
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ODOOM</t>
+          <t>J. Ellis</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -17137,7 +17147,7 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M259" t="n">
         <v>1</v>
@@ -17162,12 +17172,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MC 173</t>
+          <t>MC 251</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>MC 173</t>
+          <t>MC 251</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -17176,12 +17186,12 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>J. Ellis</t>
+          <t>I. Kwofie</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -17195,7 +17205,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -17214,7 +17224,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>MC100-A,MC100-B</t>
+          <t>MC200-A,MC200-B</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
@@ -17229,12 +17239,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MC 251</t>
+          <t>MC 261</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>MC 251</t>
+          <t>MC 261</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -17248,11 +17258,11 @@
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>I. Kwofie</t>
+          <t>E. Adu Kyeremeh</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -17262,7 +17272,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17274,7 +17284,7 @@
         <v>2</v>
       </c>
       <c r="M261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N261" t="n">
         <v>0</v>
@@ -17284,11 +17294,7 @@
           <t>MC200-A,MC200-B</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P261" t="inlineStr"/>
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr"/>
@@ -17296,12 +17302,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MC 261</t>
+          <t>MC 265</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>MC 261</t>
+          <t>MC 265</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -17315,11 +17321,11 @@
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>E. Adu Kyeremeh</t>
+          <t>D. ARHINFUL</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -17341,7 +17347,7 @@
         <v>2</v>
       </c>
       <c r="M262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N262" t="n">
         <v>0</v>
@@ -17351,7 +17357,11 @@
           <t>MC200-A,MC200-B</t>
         </is>
       </c>
-      <c r="P262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr"/>
@@ -17359,12 +17369,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MC 265</t>
+          <t>MC 267</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>MC 265</t>
+          <t>MC 267</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -17378,7 +17388,7 @@
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>D. ARHINFUL</t>
+          <t>KOMOLAFE</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -17426,12 +17436,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>MC 267</t>
+          <t>MC 273</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MC 267</t>
+          <t>MC 273</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -17445,7 +17455,7 @@
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KOMOLAFE</t>
+          <t>Ewusi-Essoun</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -17493,12 +17503,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MC 273</t>
+          <t>MC 275</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>MC 273</t>
+          <t>MC 275</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -17512,7 +17522,7 @@
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Ewusi-Essoun</t>
+          <t>J. Ellis</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -17560,12 +17570,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>MC 275</t>
+          <t>MC 277</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>MC 275</t>
+          <t>MC 277</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -17579,7 +17589,7 @@
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>J. Ellis</t>
+          <t>S. K. Yormesor</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -17627,12 +17637,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MC 277</t>
+          <t>MC 279</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>MC 277</t>
+          <t>MC 279</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -17717,10 +17727,10 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I268" t="n">
         <v>0</v>
@@ -17761,12 +17771,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MC 279</t>
+          <t>MC 361</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>MC 279</t>
+          <t>MC 361</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -17775,19 +17785,19 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>S. K. Yormesor</t>
+          <t>ANAFO</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I269" t="n">
         <v>0</v>
@@ -17803,7 +17813,7 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M269" t="n">
         <v>1</v>
@@ -17813,7 +17823,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>MC200-A,MC200-B</t>
+          <t>MC300-A,MC300-B</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
@@ -17828,12 +17838,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MC 361</t>
+          <t>MC 363</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>MC 361</t>
+          <t>MC 363</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -17847,11 +17857,11 @@
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ANAFO</t>
+          <t>NTI</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -17870,7 +17880,7 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M270" t="n">
         <v>1</v>
@@ -17895,12 +17905,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MC 363</t>
+          <t>MC 365</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>MC 363</t>
+          <t>MC 365</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -17914,11 +17924,11 @@
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>NTI</t>
+          <t>ASHUN</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -17937,7 +17947,7 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M271" t="n">
         <v>1</v>
@@ -17985,10 +17995,10 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I272" t="n">
         <v>0</v>
@@ -18000,11 +18010,11 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M272" t="n">
         <v>1</v>
@@ -18029,12 +18039,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MC 365</t>
+          <t>MC 367</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>MC 365</t>
+          <t>MC 367</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -18048,14 +18058,14 @@
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>ASHUN</t>
+          <t>AMPOMAH</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I273" t="n">
         <v>0</v>
@@ -18067,7 +18077,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L273" t="n">
@@ -18096,12 +18106,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MC 367</t>
+          <t>MC 369</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MC 367</t>
+          <t>MC 369</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -18115,7 +18125,7 @@
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>AMPOMAH</t>
+          <t>Dr G. Owusu</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -18163,12 +18173,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MC 369</t>
+          <t>MC 371</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MC 369</t>
+          <t>MC 371</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -18182,11 +18192,11 @@
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Dr G. Owusu</t>
+          <t>KOMOLAFE</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -18208,7 +18218,7 @@
         <v>2</v>
       </c>
       <c r="M275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N275" t="n">
         <v>0</v>
@@ -18218,11 +18228,7 @@
           <t>MC300-A,MC300-B</t>
         </is>
       </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P275" t="inlineStr"/>
       <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr"/>
@@ -18230,12 +18236,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MC 371</t>
+          <t>MC 373</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>MC 371</t>
+          <t>MC 373</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -18249,11 +18255,11 @@
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>KOMOLAFE</t>
+          <t>E. Adu Kyeremeh</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -18263,7 +18269,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -18272,10 +18278,10 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N276" t="n">
         <v>0</v>
@@ -18285,7 +18291,11 @@
           <t>MC300-A,MC300-B</t>
         </is>
       </c>
-      <c r="P276" t="inlineStr"/>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr"/>
@@ -18293,12 +18303,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MC 373</t>
+          <t>MC 375</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>MC 373</t>
+          <t>MC 375</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -18312,11 +18322,11 @@
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>E. Adu Kyeremeh</t>
+          <t>Ewusi-Essoun</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -18326,7 +18336,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -18335,10 +18345,10 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M277" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N277" t="n">
         <v>0</v>
@@ -18348,11 +18358,7 @@
           <t>MC300-A,MC300-B</t>
         </is>
       </c>
-      <c r="P277" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P277" t="inlineStr"/>
       <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr"/>
@@ -18360,12 +18366,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MC 375</t>
+          <t>MC 451</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>MC 375</t>
+          <t>MC 451</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -18374,16 +18380,16 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ewusi-Essoun</t>
+          <t>ADU KYEREMH</t>
         </is>
       </c>
       <c r="G278" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -18402,20 +18408,24 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N278" t="n">
         <v>0</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>MC300-A,MC300-B</t>
-        </is>
-      </c>
-      <c r="P278" t="inlineStr"/>
+          <t>MC400-A,MC400-B</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q278" t="inlineStr"/>
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr"/>
@@ -18423,12 +18433,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MC 451</t>
+          <t>MC 459</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>MC 451</t>
+          <t>MC 459</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -18442,11 +18452,11 @@
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>ADU KYEREMH</t>
+          <t>R. K. Amoah</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -18465,7 +18475,7 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M279" t="n">
         <v>1</v>
@@ -18490,12 +18500,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MC 459</t>
+          <t>MC 465</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>MC 459</t>
+          <t>MC 465</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -18509,7 +18519,7 @@
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
-          <t>R. K. Amoah</t>
+          <t>Dr E. M. Martey</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -18557,12 +18567,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MC 465</t>
+          <t>MC 467</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>MC 465</t>
+          <t>MC 467</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -18576,7 +18586,7 @@
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Dr E. M. Martey</t>
+          <t>ODOOM</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -18624,12 +18634,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MC 467</t>
+          <t>MC 471</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>MC 467</t>
+          <t>MC 471</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -18643,7 +18653,7 @@
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>ODOOM</t>
+          <t>YAKAH</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -18657,7 +18667,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -18691,12 +18701,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MC 471</t>
+          <t>MC 473</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>MC 471</t>
+          <t>MC 473</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -18710,7 +18720,7 @@
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>YAKAH</t>
+          <t>Ewusi-Essoun</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -18724,7 +18734,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -18758,30 +18768,30 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MC 473</t>
+          <t>TM 141</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>MC 473</t>
+          <t>TM 141</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Ewusi-Essoun</t>
+          <t>TORTOR</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -18800,24 +18810,14 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2</v>
-      </c>
-      <c r="M284" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M284" t="inlineStr"/>
       <c r="N284" t="n">
         <v>0</v>
       </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>MC400-A,MC400-B</t>
-        </is>
-      </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
       <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr"/>
@@ -18825,17 +18825,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MF 141</t>
+          <t>TM 141</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>MF 141</t>
+          <t>TM 141</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -18848,10 +18848,10 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I285" t="n">
         <v>0</v>
@@ -18882,12 +18882,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MF 141</t>
+          <t>MF 159</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>MF 141</t>
+          <t>MF 159</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -18901,21 +18901,21 @@
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>TORTOR</t>
+          <t>Dr A. A. Amponsah</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -18926,12 +18926,22 @@
       <c r="L286" t="n">
         <v>1</v>
       </c>
-      <c r="M286" t="inlineStr"/>
+      <c r="M286" t="n">
+        <v>1</v>
+      </c>
       <c r="N286" t="n">
         <v>0</v>
       </c>
-      <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>MF100-A</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q286" t="inlineStr"/>
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr"/>
@@ -18939,17 +18949,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TM 141</t>
+          <t>MF 163</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>TM 141</t>
+          <t>MF 163</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>MF</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -18958,11 +18968,11 @@
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>TORTOR</t>
+          <t>Dr E. M. Martey</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -18981,13 +18991,19 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>1</v>
-      </c>
-      <c r="M287" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M287" t="n">
+        <v>1</v>
+      </c>
       <c r="N287" t="n">
         <v>0</v>
       </c>
-      <c r="O287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>MF100-A</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr"/>
       <c r="Q287" t="inlineStr"/>
       <c r="R287" t="inlineStr"/>
@@ -18996,17 +19012,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TM 141</t>
+          <t>MF 169</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>TM 141</t>
+          <t>MF 169</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>MF</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -19015,14 +19031,14 @@
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>TORTOR</t>
+          <t>Owusu-Bempah</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I288" t="n">
         <v>0</v>
@@ -19038,13 +19054,19 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>1</v>
-      </c>
-      <c r="M288" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M288" t="n">
+        <v>1</v>
+      </c>
       <c r="N288" t="n">
         <v>0</v>
       </c>
-      <c r="O288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>MF100-A</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr"/>
       <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr"/>
@@ -19053,12 +19075,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MF 159</t>
+          <t>MF 171</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MF 159</t>
+          <t>MF 171</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -19072,11 +19094,11 @@
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dr A. A. Amponsah</t>
+          <t>AMPOFI</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -19086,7 +19108,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -19095,10 +19117,10 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N289" t="n">
         <v>0</v>
@@ -19108,11 +19130,7 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P289" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P289" t="inlineStr"/>
       <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr"/>
@@ -19120,12 +19138,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MF 163</t>
+          <t>MF 173</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MF 163</t>
+          <t>MF 173</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -19139,7 +19157,7 @@
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dr E. M. Martey</t>
+          <t>Owusu-Bempah</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -19153,7 +19171,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -19175,7 +19193,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q290" t="inlineStr"/>
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr"/>
@@ -19183,12 +19205,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MF 169</t>
+          <t>MF 175</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MF 169</t>
+          <t>MF 175</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -19202,11 +19224,11 @@
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Owusu-Bempah</t>
+          <t>MENSAH</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -19216,7 +19238,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -19225,7 +19247,7 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M291" t="n">
         <v>1</v>
@@ -19238,7 +19260,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P291" t="inlineStr"/>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q291" t="inlineStr"/>
       <c r="R291" t="inlineStr"/>
       <c r="S291" t="inlineStr"/>
@@ -19246,17 +19272,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>MF 171</t>
+          <t>PM 145</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MF 171</t>
+          <t>PM 145</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -19265,11 +19291,11 @@
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>AMPOFI</t>
+          <t>E. Adu Kyeremeh</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -19291,14 +19317,14 @@
         <v>2</v>
       </c>
       <c r="M292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N292" t="n">
         <v>0</v>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>MF100-A</t>
+          <t>PM100-A</t>
         </is>
       </c>
       <c r="P292" t="inlineStr"/>
@@ -19309,17 +19335,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MF 173</t>
+          <t>TM 155</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MF 173</t>
+          <t>TM 155</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -19328,7 +19354,7 @@
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Owusu-Bempah</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -19342,7 +19368,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -19361,14 +19387,10 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>MF100-A</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>TM100-A</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr"/>
       <c r="Q293" t="inlineStr"/>
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr"/>
@@ -19376,17 +19398,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MF 175</t>
+          <t>TM 159</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MF 175</t>
+          <t>TM 159</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -19395,11 +19417,11 @@
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>MENSAH</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -19418,7 +19440,7 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M294" t="n">
         <v>1</v>
@@ -19428,7 +19450,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>MF100-A</t>
+          <t>TM100-A</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -19443,17 +19465,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>PM 145</t>
+          <t>TM 161</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PM 145</t>
+          <t>TM 161</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -19462,11 +19484,11 @@
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>E. Adu Kyeremeh</t>
+          <t>Owusu-Bempah</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -19476,7 +19498,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -19485,7 +19507,7 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M295" t="n">
         <v>1</v>
@@ -19495,10 +19517,14 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>PM100-A</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr"/>
+          <t>TM100-A</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q295" t="inlineStr"/>
       <c r="R295" t="inlineStr"/>
       <c r="S295" t="inlineStr"/>
@@ -19506,12 +19532,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>TM 155</t>
+          <t>TM 163</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>TM 155</t>
+          <t>TM 163</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -19525,7 +19551,7 @@
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>S. AFFUL</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -19539,7 +19565,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -19561,7 +19587,11 @@
           <t>TM100-A</t>
         </is>
       </c>
-      <c r="P296" t="inlineStr"/>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q296" t="inlineStr"/>
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr"/>
@@ -19569,12 +19599,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TM 159</t>
+          <t>TM 167</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>TM 159</t>
+          <t>TM 167</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -19588,11 +19618,11 @@
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>J. Ellis</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -19602,7 +19632,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -19614,7 +19644,7 @@
         <v>2</v>
       </c>
       <c r="M297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N297" t="n">
         <v>0</v>
@@ -19624,211 +19654,10 @@
           <t>TM100-A</t>
         </is>
       </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="P297" t="inlineStr"/>
       <c r="Q297" t="inlineStr"/>
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>TM 161</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>TM 161</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>TM</t>
-        </is>
-      </c>
-      <c r="D298" t="n">
-        <v>100</v>
-      </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Owusu-Bempah</t>
-        </is>
-      </c>
-      <c r="G298" t="n">
-        <v>1</v>
-      </c>
-      <c r="H298" t="n">
-        <v>0</v>
-      </c>
-      <c r="I298" t="n">
-        <v>0</v>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L298" t="n">
-        <v>1</v>
-      </c>
-      <c r="M298" t="n">
-        <v>1</v>
-      </c>
-      <c r="N298" t="n">
-        <v>0</v>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>TM100-A</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="Q298" t="inlineStr"/>
-      <c r="R298" t="inlineStr"/>
-      <c r="S298" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>TM 163</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>TM 163</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>TM</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>100</v>
-      </c>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>S. AFFUL</t>
-        </is>
-      </c>
-      <c r="G299" t="n">
-        <v>2</v>
-      </c>
-      <c r="H299" t="n">
-        <v>0</v>
-      </c>
-      <c r="I299" t="n">
-        <v>0</v>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L299" t="n">
-        <v>2</v>
-      </c>
-      <c r="M299" t="n">
-        <v>1</v>
-      </c>
-      <c r="N299" t="n">
-        <v>0</v>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>TM100-A</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="Q299" t="inlineStr"/>
-      <c r="R299" t="inlineStr"/>
-      <c r="S299" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>TM 167</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>TM 167</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>TM</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>100</v>
-      </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>J. Ellis</t>
-        </is>
-      </c>
-      <c r="G300" t="n">
-        <v>4</v>
-      </c>
-      <c r="H300" t="n">
-        <v>0</v>
-      </c>
-      <c r="I300" t="n">
-        <v>0</v>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L300" t="n">
-        <v>2</v>
-      </c>
-      <c r="M300" t="n">
-        <v>2</v>
-      </c>
-      <c r="N300" t="n">
-        <v>0</v>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>TM100-A</t>
-        </is>
-      </c>
-      <c r="P300" t="inlineStr"/>
-      <c r="Q300" t="inlineStr"/>
-      <c r="R300" t="inlineStr"/>
-      <c r="S300" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
